--- a/synthetic/output/targets/targets.xlsx
+++ b/synthetic/output/targets/targets.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>179657.07</v>
+        <v>155768.51</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>193719.63</v>
+        <v>195571.63</v>
       </c>
     </row>
     <row r="4">
@@ -500,7 +500,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>52816.84</v>
+        <v>94538.03999999999</v>
       </c>
     </row>
     <row r="5">
@@ -523,7 +523,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>117422.44</v>
+        <v>50694.66</v>
       </c>
     </row>
     <row r="6">
@@ -546,7 +546,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>109004.85</v>
+        <v>54547.07</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>184880.23</v>
+        <v>109672.6</v>
       </c>
     </row>
     <row r="8">
@@ -592,7 +592,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>88632.25999999999</v>
+        <v>184699.97</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>172190.9</v>
+        <v>158889.07</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>177745.16</v>
+        <v>156386.72</v>
       </c>
     </row>
     <row r="11">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>131098.07</v>
+        <v>214672.09</v>
       </c>
     </row>
     <row r="12">
@@ -684,7 +684,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>135540.65</v>
+        <v>99502.41</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>115585.33</v>
+        <v>119231.95</v>
       </c>
     </row>
     <row r="14">
@@ -730,7 +730,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>130166.65</v>
+        <v>105129.95</v>
       </c>
     </row>
     <row r="15">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>69077.02</v>
+        <v>237482.07</v>
       </c>
     </row>
     <row r="16">
@@ -776,7 +776,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>246337.04</v>
+        <v>195004.79</v>
       </c>
     </row>
     <row r="17">
@@ -799,7 +799,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>145490.82</v>
+        <v>72568.92999999999</v>
       </c>
     </row>
     <row r="18">
@@ -822,7 +822,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>237165.08</v>
+        <v>211895.64</v>
       </c>
     </row>
     <row r="19">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>51366.02</v>
+        <v>133848.12</v>
       </c>
     </row>
     <row r="20">
@@ -868,7 +868,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>126714.88</v>
+        <v>203210.69</v>
       </c>
     </row>
     <row r="21">
@@ -891,7 +891,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>139347.1</v>
+        <v>226751.32</v>
       </c>
     </row>
     <row r="22">
@@ -914,7 +914,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103398.87</v>
+        <v>53129.16</v>
       </c>
     </row>
     <row r="23">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>115925.06</v>
+        <v>91216.32000000001</v>
       </c>
     </row>
     <row r="24">
@@ -960,7 +960,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>166492.15</v>
+        <v>70179.34</v>
       </c>
     </row>
     <row r="25">
@@ -983,7 +983,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>164575.47</v>
+        <v>56715.26</v>
       </c>
     </row>
     <row r="26">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102310.63</v>
+        <v>169556.98</v>
       </c>
     </row>
     <row r="27">
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>121910.42</v>
+        <v>190657.25</v>
       </c>
     </row>
     <row r="28">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>P024</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>97260.52</v>
+        <v>59735.26</v>
       </c>
     </row>
     <row r="29">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>183557.22</v>
+        <v>198108.22</v>
       </c>
     </row>
     <row r="30">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>187214.72</v>
+        <v>93453.84</v>
       </c>
     </row>
     <row r="31">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>234621.2</v>
+        <v>222746.05</v>
       </c>
     </row>
     <row r="32">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>227560.28</v>
+        <v>61288.81</v>
       </c>
     </row>
     <row r="33">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>203968.21</v>
+        <v>150779.17</v>
       </c>
     </row>
     <row r="34">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>188058.08</v>
+        <v>107852.69</v>
       </c>
     </row>
     <row r="35">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>177742.27</v>
+        <v>213157.25</v>
       </c>
     </row>
     <row r="36">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>238127.12</v>
+        <v>196303.5</v>
       </c>
     </row>
     <row r="37">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>123508.78</v>
+        <v>113780.74</v>
       </c>
     </row>
     <row r="38">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>94169.85000000001</v>
+        <v>169583.53</v>
       </c>
     </row>
     <row r="39">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>241472.11</v>
+        <v>184506.38</v>
       </c>
     </row>
     <row r="40">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>145636.38</v>
+        <v>114133.02</v>
       </c>
     </row>
     <row r="41">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>140995.73</v>
+        <v>110352.89</v>
       </c>
     </row>
     <row r="42">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>247767.59</v>
+        <v>78652.09</v>
       </c>
     </row>
     <row r="43">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>124724.97</v>
+        <v>182042.48</v>
       </c>
     </row>
     <row r="44">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>190388.15</v>
+        <v>94208.55</v>
       </c>
     </row>
     <row r="45">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>232559.38</v>
+        <v>110100.19</v>
       </c>
     </row>
     <row r="46">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>201470.1</v>
+        <v>62191.53</v>
       </c>
     </row>
     <row r="47">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>210399</v>
+        <v>239704.05</v>
       </c>
     </row>
     <row r="48">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>215120.7</v>
+        <v>225942.78</v>
       </c>
     </row>
     <row r="49">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>202371.92</v>
+        <v>232315.53</v>
       </c>
     </row>
     <row r="50">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>186068.38</v>
+        <v>175198.63</v>
       </c>
     </row>
     <row r="51">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>169162.89</v>
+        <v>135440.12</v>
       </c>
     </row>
     <row r="52">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>207474.14</v>
+        <v>149124.16</v>
       </c>
     </row>
     <row r="53">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>155101.33</v>
+        <v>244458.05</v>
       </c>
     </row>
     <row r="54">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>155634.62</v>
+        <v>238317.28</v>
       </c>
     </row>
     <row r="55">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>122356.97</v>
+        <v>184268.5</v>
       </c>
     </row>
     <row r="56">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>233448.94</v>
+        <v>207160.92</v>
       </c>
     </row>
     <row r="57">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>72441.75999999999</v>
+        <v>113746.89</v>
       </c>
     </row>
     <row r="58">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>90431.36</v>
+        <v>86775.8</v>
       </c>
     </row>
     <row r="59">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>157332.03</v>
+        <v>157585.65</v>
       </c>
     </row>
     <row r="60">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>82907.42999999999</v>
+        <v>98193.64</v>
       </c>
     </row>
     <row r="61">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220897.2</v>
+        <v>95068.91</v>
       </c>
     </row>
     <row r="62">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>138368.11</v>
+        <v>221508.25</v>
       </c>
     </row>
     <row r="63">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>186059.05</v>
+        <v>78870.35000000001</v>
       </c>
     </row>
     <row r="64">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>193383.59</v>
+        <v>142605.03</v>
       </c>
     </row>
     <row r="65">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>147765.59</v>
+        <v>61524.79</v>
       </c>
     </row>
     <row r="66">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229777.87</v>
+        <v>132535.5</v>
       </c>
     </row>
     <row r="67">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>139096.54</v>
+        <v>133301.57</v>
       </c>
     </row>
     <row r="68">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>61127.16</v>
+        <v>155998.36</v>
       </c>
     </row>
     <row r="69">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2004,7 +2004,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>76388.87</v>
+        <v>127683.81</v>
       </c>
     </row>
     <row r="70">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>133084.91</v>
+        <v>100999.13</v>
       </c>
     </row>
     <row r="71">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>162782.24</v>
+        <v>116052.6</v>
       </c>
     </row>
     <row r="72">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>161759.44</v>
+        <v>65814.09</v>
       </c>
     </row>
     <row r="73">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>184553.54</v>
+        <v>139957.37</v>
       </c>
     </row>
     <row r="74">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>111633.91</v>
+        <v>124215.5</v>
       </c>
     </row>
     <row r="75">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>54354.09</v>
+        <v>157127.11</v>
       </c>
     </row>
     <row r="76">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100891.44</v>
+        <v>215881.26</v>
       </c>
     </row>
     <row r="77">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>50603.09</v>
+        <v>60307.33</v>
       </c>
     </row>
     <row r="78">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>93580.25999999999</v>
+        <v>125433.59</v>
       </c>
     </row>
     <row r="79">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>64605.91</v>
+        <v>170993.89</v>
       </c>
     </row>
     <row r="80">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>134739.48</v>
+        <v>57909.51</v>
       </c>
     </row>
     <row r="81">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>190076.98</v>
+        <v>64556.87</v>
       </c>
     </row>
     <row r="82">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>158232.7</v>
+        <v>210930.12</v>
       </c>
     </row>
     <row r="83">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>62051.13</v>
+        <v>167516.74</v>
       </c>
     </row>
     <row r="84">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228843.69</v>
+        <v>184290.1</v>
       </c>
     </row>
     <row r="85">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>247227.45</v>
+        <v>93403.3</v>
       </c>
     </row>
     <row r="86">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>85996.27</v>
+        <v>110637.61</v>
       </c>
     </row>
     <row r="87">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P028</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>77085.77</v>
+        <v>231798.83</v>
       </c>
     </row>
     <row r="88">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>178305</v>
+        <v>92361.55</v>
       </c>
     </row>
     <row r="89">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>195857.9</v>
+        <v>88004.74000000001</v>
       </c>
     </row>
     <row r="90">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>242756.51</v>
+        <v>198295.04</v>
       </c>
     </row>
     <row r="91">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P028</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>124892.18</v>
+        <v>199375.85</v>
       </c>
     </row>
     <row r="92">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228266.72</v>
+        <v>200866.15</v>
       </c>
     </row>
     <row r="93">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>139707.43</v>
+        <v>232888.26</v>
       </c>
     </row>
     <row r="94">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>233423.02</v>
+        <v>189125.26</v>
       </c>
     </row>
     <row r="95">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P028</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>125499.27</v>
+        <v>190753.72</v>
       </c>
     </row>
     <row r="96">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>66050</v>
+        <v>129326.41</v>
       </c>
     </row>
     <row r="97">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>242828.88</v>
+        <v>97866.19</v>
       </c>
     </row>
     <row r="98">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>224910.74</v>
+        <v>114323</v>
       </c>
     </row>
     <row r="99">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P028</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>76597.96000000001</v>
+        <v>106611.84</v>
       </c>
     </row>
     <row r="100">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222057.32</v>
+        <v>143250.09</v>
       </c>
     </row>
     <row r="101">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>73726.63</v>
+        <v>179744.27</v>
       </c>
     </row>
     <row r="102">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>248569.36</v>
+        <v>111684.46</v>
       </c>
     </row>
     <row r="103">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P028</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>128611.73</v>
+        <v>121928.92</v>
       </c>
     </row>
     <row r="104">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>75469.42</v>
+        <v>226562.39</v>
       </c>
     </row>
     <row r="105">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>245744.88</v>
+        <v>143200.81</v>
       </c>
     </row>
     <row r="106">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>216964.32</v>
+        <v>210563.32</v>
       </c>
     </row>
     <row r="107">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P028</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>201235.88</v>
+        <v>194482.71</v>
       </c>
     </row>
     <row r="108">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>245698.14</v>
+        <v>202325.79</v>
       </c>
     </row>
     <row r="109">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>142600.78</v>
+        <v>114046.66</v>
       </c>
     </row>
     <row r="110">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>193818.8</v>
+        <v>90625.5</v>
       </c>
     </row>
     <row r="111">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P028</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>134825.61</v>
+        <v>112584.4</v>
       </c>
     </row>
     <row r="112">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>125855.29</v>
+        <v>59143.09</v>
       </c>
     </row>
     <row r="113">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>95932.81</v>
+        <v>222816.97</v>
       </c>
     </row>
     <row r="114">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P024</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>87696.09</v>
+        <v>160662.31</v>
       </c>
     </row>
     <row r="115">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>225041.63</v>
+        <v>166806.38</v>
       </c>
     </row>
     <row r="116">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>203097.99</v>
+        <v>194002.39</v>
       </c>
     </row>
     <row r="117">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>56443.46</v>
+        <v>109038.46</v>
       </c>
     </row>
     <row r="118">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P024</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>182039.54</v>
+        <v>89238.36</v>
       </c>
     </row>
     <row r="119">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>172984.64</v>
+        <v>96003.73</v>
       </c>
     </row>
     <row r="120">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>237247.59</v>
+        <v>163957.9</v>
       </c>
     </row>
     <row r="121">
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>227808.27</v>
+        <v>99146</v>
       </c>
     </row>
     <row r="122">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P024</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>98133.25999999999</v>
+        <v>160128.51</v>
       </c>
     </row>
     <row r="123">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>63458.18</v>
+        <v>238692.91</v>
       </c>
     </row>
     <row r="124">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>168788.83</v>
+        <v>117512.86</v>
       </c>
     </row>
     <row r="125">
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>139288.21</v>
+        <v>202672.13</v>
       </c>
     </row>
     <row r="126">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P024</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>184404.73</v>
+        <v>147724.22</v>
       </c>
     </row>
     <row r="127">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>224442.48</v>
+        <v>194711.59</v>
       </c>
     </row>
     <row r="128">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3361,7 +3361,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>98946.83</v>
+        <v>197918.82</v>
       </c>
     </row>
     <row r="129">
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>58847.35</v>
+        <v>142165.8</v>
       </c>
     </row>
     <row r="130">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P024</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>137792.56</v>
+        <v>196554.45</v>
       </c>
     </row>
     <row r="131">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>157951.96</v>
+        <v>120435.23</v>
       </c>
     </row>
     <row r="132">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>200877.14</v>
+        <v>77991.71000000001</v>
       </c>
     </row>
     <row r="133">
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>205212.72</v>
+        <v>159309.27</v>
       </c>
     </row>
     <row r="134">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P024</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>78027.12</v>
+        <v>86809.55</v>
       </c>
     </row>
     <row r="135">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3522,7 +3522,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>248696.69</v>
+        <v>227872.91</v>
       </c>
     </row>
     <row r="136">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>96832.3</v>
+        <v>248064.71</v>
       </c>
     </row>
     <row r="137">
@@ -3568,7 +3568,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>233279.41</v>
+        <v>241447.38</v>
       </c>
     </row>
     <row r="138">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P024</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>165222.07</v>
+        <v>154788.88</v>
       </c>
     </row>
     <row r="139">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>165494.96</v>
+        <v>217813.7</v>
       </c>
     </row>
     <row r="140">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>204507.64</v>
+        <v>64866.08</v>
       </c>
     </row>
     <row r="141">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>213676.5</v>
+        <v>213599.18</v>
       </c>
     </row>
     <row r="142">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>247139.11</v>
+        <v>77498.31</v>
       </c>
     </row>
     <row r="143">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>154250.21</v>
+        <v>176140.33</v>
       </c>
     </row>
     <row r="144">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>132712.04</v>
+        <v>63593.59</v>
       </c>
     </row>
     <row r="145">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>105030.78</v>
+        <v>80205.92999999999</v>
       </c>
     </row>
     <row r="146">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>161343.62</v>
+        <v>93743.92999999999</v>
       </c>
     </row>
     <row r="147">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>168333.42</v>
+        <v>141201.93</v>
       </c>
     </row>
     <row r="148">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>197042.42</v>
+        <v>62090.02</v>
       </c>
     </row>
     <row r="149">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3844,7 +3844,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>85026.64</v>
+        <v>177545.72</v>
       </c>
     </row>
     <row r="150">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185750.02</v>
+        <v>236780.74</v>
       </c>
     </row>
     <row r="151">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>161170.13</v>
+        <v>232550.29</v>
       </c>
     </row>
     <row r="152">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>59376.82</v>
+        <v>181856.87</v>
       </c>
     </row>
     <row r="153">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -3936,7 +3936,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>118882.97</v>
+        <v>53146.35</v>
       </c>
     </row>
     <row r="154">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>178663.21</v>
+        <v>156442.5</v>
       </c>
     </row>
     <row r="155">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>126230.93</v>
+        <v>132267.7</v>
       </c>
     </row>
     <row r="156">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>154892.61</v>
+        <v>53345.23</v>
       </c>
     </row>
     <row r="157">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>189261.68</v>
+        <v>194438.54</v>
       </c>
     </row>
     <row r="158">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>131651.84</v>
+        <v>157147.62</v>
       </c>
     </row>
     <row r="159">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>109977.7</v>
+        <v>107337.71</v>
       </c>
     </row>
     <row r="160">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>86775.8</v>
+        <v>150443.21</v>
       </c>
     </row>
     <row r="161">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>157585.65</v>
+        <v>189571.82</v>
       </c>
     </row>
     <row r="162">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>98193.64</v>
+        <v>136114.64</v>
       </c>
     </row>
     <row r="163">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4166,7 +4166,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>95068.91</v>
+        <v>237942.38</v>
       </c>
     </row>
     <row r="164">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221508.25</v>
+        <v>85853.37</v>
       </c>
     </row>
     <row r="165">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>78870.35000000001</v>
+        <v>233609.77</v>
       </c>
     </row>
     <row r="166">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>142605.03</v>
+        <v>154877.08</v>
       </c>
     </row>
     <row r="167">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>61524.79</v>
+        <v>98193.77</v>
       </c>
     </row>
     <row r="168">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>P029</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>132535.5</v>
+        <v>173956.17</v>
       </c>
     </row>
     <row r="169">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4304,7 +4304,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>133301.57</v>
+        <v>100483.64</v>
       </c>
     </row>
     <row r="170">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100999.13</v>
+        <v>65803.85000000001</v>
       </c>
     </row>
     <row r="171">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -4350,7 +4350,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>116052.6</v>
+        <v>241859.56</v>
       </c>
     </row>
     <row r="172">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>65814.09</v>
+        <v>141799.55</v>
       </c>
     </row>
     <row r="173">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>139957.37</v>
+        <v>98641.58</v>
       </c>
     </row>
     <row r="174">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -4419,7 +4419,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>124215.5</v>
+        <v>189447.26</v>
       </c>
     </row>
     <row r="175">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>157127.11</v>
+        <v>109994.93</v>
       </c>
     </row>
     <row r="176">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>215881.26</v>
+        <v>215612.42</v>
       </c>
     </row>
     <row r="177">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>60307.33</v>
+        <v>66123.38</v>
       </c>
     </row>
     <row r="178">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>125433.59</v>
+        <v>248334.94</v>
       </c>
     </row>
     <row r="179">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>170993.89</v>
+        <v>179978.89</v>
       </c>
     </row>
     <row r="180">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>57909.51</v>
+        <v>56336.9</v>
       </c>
     </row>
     <row r="181">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>64556.87</v>
+        <v>131055.66</v>
       </c>
     </row>
     <row r="182">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>210930.12</v>
+        <v>125433.91</v>
       </c>
     </row>
     <row r="183">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>167516.74</v>
+        <v>145201.02</v>
       </c>
     </row>
     <row r="184">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>184290.1</v>
+        <v>177349.62</v>
       </c>
     </row>
     <row r="185">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>93403.3</v>
+        <v>190569.03</v>
       </c>
     </row>
     <row r="186">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>91777.82000000001</v>
+        <v>66537.22</v>
       </c>
     </row>
     <row r="187">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>231406.57</v>
+        <v>219065.96</v>
       </c>
     </row>
     <row r="188">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>110637.61</v>
+        <v>178981.45</v>
       </c>
     </row>
     <row r="189">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>231798.83</v>
+        <v>116254.12</v>
       </c>
     </row>
     <row r="190">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>92361.55</v>
+        <v>245465.84</v>
       </c>
     </row>
     <row r="191">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>88004.74000000001</v>
+        <v>244767.95</v>
       </c>
     </row>
     <row r="192">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>198295.04</v>
+        <v>228958.24</v>
       </c>
     </row>
     <row r="193">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>199375.85</v>
+        <v>233830.44</v>
       </c>
     </row>
     <row r="194">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>200866.15</v>
+        <v>95953.3</v>
       </c>
     </row>
     <row r="195">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>232888.26</v>
+        <v>230254.59</v>
       </c>
     </row>
     <row r="196">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P026</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>189125.26</v>
+        <v>188457.54</v>
       </c>
     </row>
     <row r="197">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -4948,7 +4948,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>190753.72</v>
+        <v>163356.83</v>
       </c>
     </row>
     <row r="198">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>114323</v>
+        <v>186885.75</v>
       </c>
     </row>
     <row r="199">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>106611.84</v>
+        <v>106074.6</v>
       </c>
     </row>
     <row r="200">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>143250.09</v>
+        <v>158606.14</v>
       </c>
     </row>
     <row r="201">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>179744.27</v>
+        <v>181621.85</v>
       </c>
     </row>
     <row r="202">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>111684.46</v>
+        <v>85870.89999999999</v>
       </c>
     </row>
     <row r="203">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>121928.92</v>
+        <v>220085.52</v>
       </c>
     </row>
     <row r="204">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>226562.39</v>
+        <v>53131.62</v>
       </c>
     </row>
     <row r="205">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5132,7 +5132,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>143200.81</v>
+        <v>91431.62</v>
       </c>
     </row>
     <row r="206">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>210563.32</v>
+        <v>78838.31</v>
       </c>
     </row>
     <row r="207">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>194482.71</v>
+        <v>214138.15</v>
       </c>
     </row>
     <row r="208">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>202325.79</v>
+        <v>214180.48</v>
       </c>
     </row>
     <row r="209">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>114046.66</v>
+        <v>235774.99</v>
       </c>
     </row>
     <row r="210">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>90625.5</v>
+        <v>109855.38</v>
       </c>
     </row>
     <row r="211">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>112584.4</v>
+        <v>162791.64</v>
       </c>
     </row>
     <row r="212">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>59143.09</v>
+        <v>163339.18</v>
       </c>
     </row>
     <row r="213">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -5316,7 +5316,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>222816.97</v>
+        <v>219888.49</v>
       </c>
     </row>
     <row r="214">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>198250.48</v>
+        <v>185406.99</v>
       </c>
     </row>
     <row r="215">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>53243.98</v>
+        <v>158112.49</v>
       </c>
     </row>
     <row r="216">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -5385,7 +5385,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>160662.31</v>
+        <v>126769.24</v>
       </c>
     </row>
     <row r="217">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>166806.38</v>
+        <v>197949.03</v>
       </c>
     </row>
     <row r="218">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>194002.39</v>
+        <v>208099.62</v>
       </c>
     </row>
     <row r="219">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>109038.46</v>
+        <v>187862.11</v>
       </c>
     </row>
     <row r="220">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>89238.36</v>
+        <v>65685.53999999999</v>
       </c>
     </row>
     <row r="221">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -5500,7 +5500,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>96003.73</v>
+        <v>199091.31</v>
       </c>
     </row>
     <row r="222">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>163957.9</v>
+        <v>119171.9</v>
       </c>
     </row>
     <row r="223">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>P030</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -5546,7 +5546,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>99146</v>
+        <v>69537.16</v>
       </c>
     </row>
     <row r="224">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P030</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>160128.51</v>
+        <v>96428.8</v>
       </c>
     </row>
     <row r="225">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>238692.91</v>
+        <v>65203.65</v>
       </c>
     </row>
     <row r="226">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>147724.22</v>
+        <v>55925.13</v>
       </c>
     </row>
     <row r="227">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>194711.59</v>
+        <v>104665.41</v>
       </c>
     </row>
     <row r="228">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>197918.82</v>
+        <v>248517.18</v>
       </c>
     </row>
     <row r="229">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -5684,7 +5684,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>142165.8</v>
+        <v>148120.69</v>
       </c>
     </row>
     <row r="230">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>196554.45</v>
+        <v>121162.24</v>
       </c>
     </row>
     <row r="231">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>120435.23</v>
+        <v>238228.57</v>
       </c>
     </row>
     <row r="232">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>77991.71000000001</v>
+        <v>136369.59</v>
       </c>
     </row>
     <row r="233">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>159309.27</v>
+        <v>185938.97</v>
       </c>
     </row>
     <row r="234">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>86809.55</v>
+        <v>182134.38</v>
       </c>
     </row>
     <row r="235">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -5822,7 +5822,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>227872.91</v>
+        <v>67138.82000000001</v>
       </c>
     </row>
     <row r="236">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>248064.71</v>
+        <v>173723.18</v>
       </c>
     </row>
     <row r="237">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>241447.38</v>
+        <v>209611.03</v>
       </c>
     </row>
     <row r="238">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>154788.88</v>
+        <v>192621.71</v>
       </c>
     </row>
     <row r="239">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>217813.7</v>
+        <v>66407.60000000001</v>
       </c>
     </row>
     <row r="240">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>64866.08</v>
+        <v>80844.19</v>
       </c>
     </row>
     <row r="241">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>213599.18</v>
+        <v>192335.43</v>
       </c>
     </row>
     <row r="242">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>59702.88</v>
+        <v>176780.18</v>
       </c>
     </row>
     <row r="243">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>51276.76</v>
+        <v>197931.06</v>
       </c>
     </row>
     <row r="244">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>77498.31</v>
+        <v>113335.65</v>
       </c>
     </row>
     <row r="245">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>176140.33</v>
+        <v>71310.17999999999</v>
       </c>
     </row>
     <row r="246">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>63593.59</v>
+        <v>51039.04</v>
       </c>
     </row>
     <row r="247">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>80205.92999999999</v>
+        <v>111653.49</v>
       </c>
     </row>
     <row r="248">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>93743.92999999999</v>
+        <v>121983.5</v>
       </c>
     </row>
     <row r="249">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>141201.93</v>
+        <v>103953.29</v>
       </c>
     </row>
     <row r="250">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>62090.02</v>
+        <v>76501.39999999999</v>
       </c>
     </row>
     <row r="251">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P025</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -6190,7 +6190,7 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>177545.72</v>
+        <v>87478.36</v>
       </c>
     </row>
     <row r="252">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>P025</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -6213,7 +6213,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>236780.74</v>
+        <v>139768.74</v>
       </c>
     </row>
     <row r="253">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>P027</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>232550.29</v>
+        <v>160948</v>
       </c>
     </row>
     <row r="254">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>160328.71</v>
+        <v>120782.86</v>
       </c>
     </row>
     <row r="255">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>52370.19</v>
+        <v>68612.85000000001</v>
       </c>
     </row>
     <row r="256">
@@ -6305,7 +6305,7 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>155883.53</v>
+        <v>169608.76</v>
       </c>
     </row>
     <row r="257">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>104948.15</v>
+        <v>114886.07</v>
       </c>
     </row>
     <row r="258">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="E258" t="n">
-        <v>245495.87</v>
+        <v>127047.58</v>
       </c>
     </row>
     <row r="259">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>53428.52</v>
+        <v>108369.47</v>
       </c>
     </row>
     <row r="260">
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>212631.44</v>
+        <v>127559.91</v>
       </c>
     </row>
     <row r="261">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="E261" t="n">
-        <v>184806.59</v>
+        <v>66939.89999999999</v>
       </c>
     </row>
     <row r="262">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6443,7 +6443,7 @@
         </is>
       </c>
       <c r="E262" t="n">
-        <v>211233.54</v>
+        <v>230227.21</v>
       </c>
     </row>
     <row r="263">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -6466,7 +6466,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>231954.67</v>
+        <v>231041.51</v>
       </c>
     </row>
     <row r="264">
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>71403.28999999999</v>
+        <v>245634.61</v>
       </c>
     </row>
     <row r="265">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>69262.78</v>
+        <v>164392.09</v>
       </c>
     </row>
     <row r="266">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>79779.5</v>
+        <v>83916.58</v>
       </c>
     </row>
     <row r="267">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>88386.41</v>
+        <v>126146.4</v>
       </c>
     </row>
     <row r="268">
@@ -6581,7 +6581,7 @@
         </is>
       </c>
       <c r="E268" t="n">
-        <v>155291.2</v>
+        <v>77768.00999999999</v>
       </c>
     </row>
     <row r="269">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>213042.88</v>
+        <v>110226.25</v>
       </c>
     </row>
     <row r="270">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -6627,7 +6627,7 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>103464.95</v>
+        <v>148624.79</v>
       </c>
     </row>
     <row r="271">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>129379.28</v>
+        <v>62653.43</v>
       </c>
     </row>
     <row r="272">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>124610.32</v>
+        <v>136935.25</v>
       </c>
     </row>
     <row r="273">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>131205.48</v>
+        <v>134220.47</v>
       </c>
     </row>
     <row r="274">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>163000.44</v>
+        <v>146846.26</v>
       </c>
     </row>
     <row r="275">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>248046.61</v>
+        <v>65384.27</v>
       </c>
     </row>
     <row r="276">
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>95171.45</v>
+        <v>100339.95</v>
       </c>
     </row>
     <row r="277">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>186808.33</v>
+        <v>99318.00999999999</v>
       </c>
     </row>
     <row r="278">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>219573.42</v>
+        <v>175006.74</v>
       </c>
     </row>
     <row r="279">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>180747.14</v>
+        <v>168761.28</v>
       </c>
     </row>
     <row r="280">
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>221643.83</v>
+        <v>89109.64</v>
       </c>
     </row>
     <row r="281">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>201917.17</v>
+        <v>71394.47</v>
       </c>
     </row>
   </sheetData>
